--- a/jogos_2024-10-01.xlsx
+++ b/jogos_2024-10-01.xlsx
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.62</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['24', '66', '70', '75']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.77</v>
+        <v>2.03</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45566.57291666666</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['24', '66', '70', '75']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.03</v>
+        <v>2.77</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45566.57291666666</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.25</v>
       </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45566.64583333334</v>
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Horn</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="N12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.05</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['11', '19', '46']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['38', '45+1', '51', '55', '90', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45566.64583333334</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Horn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['11', '19', '46']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['38', '45+1', '51', '55', '90', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2.38</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45566.64583333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,16 +2191,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>3.68</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="Z14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['11', '49', '81']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45566.65625</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45566.65625</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
         <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['11', '48', '84']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['12', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45566.65625</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.42</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="AC17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['10', '37']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['45', '54']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['25', '36', '71']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45566.65625</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
         <v>1.4</v>
@@ -2757,59 +2757,59 @@
         <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.28</v>
       </c>
-      <c r="X18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45566.65625</v>
@@ -2836,54 +2836,54 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
       </c>
       <c r="T19" t="n">
         <v>2.75</v>
@@ -2892,53 +2892,53 @@
         <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['30', '57', '67']</t>
+          <t>['90+1', '90+3']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['79', '90+4']</t>
+          <t>['6', '23', '60', '83']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45566.65625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,65 +2991,65 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.44</v>
       </c>
-      <c r="M20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
-        <v>4.82</v>
+        <v>3.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45566.65625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.85</v>
+        <v>2.02</v>
       </c>
       <c r="M21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N21" t="n">
         <v>3.65</v>
       </c>
-      <c r="N21" t="n">
-        <v>1.93</v>
-      </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
         <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X21" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['44', '86']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45566.65625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>5.28</v>
       </c>
       <c r="R22" t="n">
         <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>['40', '55']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45566.65625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.22</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['11', '48', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45566.65625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AB24" t="n">
         <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="n">
         <v>2.2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['11', '49', '81']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45566.65625</v>
@@ -3610,16 +3610,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -3636,65 +3636,65 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.28</v>
+        <v>5.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X25" t="n">
-        <v>3.2</v>
+        <v>4.82</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['40', '55']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45566.65625</v>
@@ -3739,48 +3739,48 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="O26" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -3789,37 +3789,37 @@
         <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
         <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AA26" t="n">
         <v>3.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['44', '86']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45566.65625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>3.85</v>
+        <v>3.57</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '36', '71']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.82</v>
       </c>
-      <c r="AI27" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45566.65625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O28" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.36</v>
       </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="X28" t="n">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.91</v>
+        <v>3.45</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['90+1', '90+3']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['6', '23', '60', '83']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45566.65625</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Carlisle United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,22 +4152,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>2.35</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
         <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
         <v>1.3</v>
@@ -4185,50 +4185,50 @@
         <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X29" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AD29" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['10', '34']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45566.65625</v>
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -4281,28 +4281,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P30" t="n">
         <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
         <v>2.63</v>
@@ -4314,10 +4314,10 @@
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="Y30" t="n">
         <v>1.73</v>
@@ -4326,38 +4326,38 @@
         <v>2</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['58', '89']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['47', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45566.65625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,19 +4384,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="O31" t="n">
         <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.25</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X31" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['30', '57', '67']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79', '90+4']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45566.65625</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4528,94 +4528,94 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>3.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.1</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['10', '37']</t>
+          <t>['14', '50']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['45', '54']</t>
+          <t>['19', '37']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.19</v>
+        <v>1.72</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45566.65625</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.94</v>
+        <v>3.85</v>
       </c>
       <c r="M33" t="n">
         <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>1.94</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.3</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.19</v>
-      </c>
       <c r="X33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['35', '45+2', '45+4', '87', '90']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45566.65625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O34" t="n">
         <v>3.2</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>2.97</v>
+        <v>4.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['12', '90+2']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45566.65625</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,28 +4926,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.95</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.33</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P35" t="n">
         <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
         <v>2.63</v>
@@ -4956,25 +4956,25 @@
         <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X35" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AC35" t="n">
         <v>1.62</v>
@@ -4984,25 +4984,25 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['10', '26', '67']</t>
+          <t>['58', '89']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['47', '85']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45566.65625</v>
@@ -5029,22 +5029,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P36" t="n">
         <v>2.1</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X36" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['69', '80']</t>
+          <t>['14', '45']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['25', '51', '57', '67', '85', '90+4']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45566.65625</v>
@@ -5158,109 +5158,109 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Carlisle United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O37" t="n">
         <v>3</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O37" t="n">
-        <v>4.5</v>
-      </c>
       <c r="P37" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['35', '45+2', '45+4', '87', '90']</t>
+          <t>['10', '34']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45566.65625</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,55 +5313,55 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="O38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
         <v>2.75</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X38" t="n">
         <v>3.25</v>
       </c>
-      <c r="U38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.22</v>
-      </c>
       <c r="Y38" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC38" t="n">
         <v>1.83</v>
@@ -5371,25 +5371,25 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['14', '45']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['25', '51', '57', '67', '85', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45566.65625</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U40" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V40" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.28</v>
       </c>
-      <c r="X40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['10', '26', '67']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['14', '50']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['19', '37']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45566.65625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,16 +5674,16 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>1</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD41" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['69', '80']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45566.65625</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5818,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5829,34 +5829,34 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S42" t="n">
         <v>2.75</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
@@ -5865,47 +5865,47 @@
         <v>1.27</v>
       </c>
       <c r="X42" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="AB42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.24</v>
       </c>
-      <c r="AC42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45566.65625</v>
@@ -5932,109 +5932,109 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="M43" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="O43" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="P43" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="T43" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="U43" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X43" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['11', '59', '71', '81']</t>
+          <t>['7', '11', '29', '40', '42', '66', '79']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AJ43" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45566.66666666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
         <v>1</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
         <v>4.75</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U44" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V44" t="n">
         <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X44" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['23', '42', '82']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45566.66666666666</v>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z45" t="n">
         <v>2.25</v>
       </c>
-      <c r="U45" t="n">
+      <c r="AA45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH45" t="n">
         <v>1.57</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X45" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['7', '11', '29', '40', '42', '66', '79']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AI45" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45566.66666666666</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O46" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
         <v>4.75</v>
       </c>
       <c r="R46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V46" t="n">
         <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X46" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['23', '42', '82']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45566.66666666666</v>
@@ -6835,91 +6835,91 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G50" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>10</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA50" t="n">
         <v>2</v>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AB50" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['20', '35']</t>
+          <t>['11', '59', '71', '81']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6928,16 +6928,16 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.15</v>
+        <v>5.3</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45566.66666666666</v>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="M51" t="n">
         <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="P51" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T51" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U51" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W51" t="n">
         <v>1.18</v>
       </c>
       <c r="X51" t="n">
-        <v>5.1</v>
+        <v>3.84</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AC51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['20', '35']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ51" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45566.66666666666</v>
